--- a/tsrtsV5_final_full_sem_epg/urls_geral.xlsx
+++ b/tsrtsV5_final_full_sem_epg/urls_geral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos\thestreamremainsthesame\tsrtsV5_final_full_sem_epg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05352F85-F6BD-4AA0-9DC4-547F71DF24E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C733E78B-C8F2-4BFA-A405-42D250A0DDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="153">
   <si>
     <t>urls_reduced</t>
   </si>
@@ -109,15 +109,6 @@
     <t>https://raw.githubusercontent.com/helenfernanda/gratis/main/distrotv.xml</t>
   </si>
   <si>
-    <t>https://www.bevy.be/bevyfiles/argentina.xml</t>
-  </si>
-  <si>
-    <t>https://www.bevy.be/bevyfiles/argentinapremium.xml</t>
-  </si>
-  <si>
-    <t>https://www.bevy.be/bevyfiles/argentinapremium2.xml</t>
-  </si>
-  <si>
     <t>https://www.bevy.be/bevyfiles/australia.xml</t>
   </si>
   <si>
@@ -161,18 +152,6 @@
   </si>
   <si>
     <t>https://www.bevy.be/bevyfiles/canadapremium3.xml</t>
-  </si>
-  <si>
-    <t>https://www.bevy.be/bevyfiles/china.xml</t>
-  </si>
-  <si>
-    <t>https://www.bevy.be/bevyfiles/chinapremium.xml</t>
-  </si>
-  <si>
-    <t>https://www.bevy.be/bevyfiles/chinapremium1.xml</t>
-  </si>
-  <si>
-    <t>https://www.bevy.be/bevyfiles/chinapremium2.xml</t>
   </si>
   <si>
     <t>https://www.bevy.be/bevyfiles/denmark.xml</t>
@@ -1084,7 +1063,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1577,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="60.5546875" customWidth="1"/>
@@ -1610,7 +1589,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -1870,66 +1849,31 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1950,387 +1894,387 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
